--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:32</t>
+          <t>2026-08-26 11:20:31</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-26 11:20:31</t>
+          <t>2026-08-27 20:51:27</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-27 20:51:27</t>
+          <t>2026-08-28 21:17:21</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:17:21</t>
+          <t>2026-08-29 15:22:51</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-29 15:22:51</t>
+          <t>2026-08-30 15:07:04</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-30 15:07:04</t>
+          <t>2026-08-31 17:46:22</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-08-31 17:46:22</t>
+          <t>2026-09-01 15:18:38</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:18:38</t>
+          <t>2026-09-02 14:48:41</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-02 14:48:41</t>
+          <t>2026-09-03 14:49:02</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:49:02</t>
+          <t>2026-09-04 14:37:27</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-04 14:37:27</t>
+          <t>2026-09-05 13:36:45</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,20 +489,30 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>Days_Remaining_To_Claim</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Claim_Urgency_Tier</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -571,24 +581,32 @@
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="n">
+        <v>306</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -655,24 +673,32 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="n">
+        <v>313</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -739,24 +765,32 @@
           <t>2024-07-30</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>327</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>
@@ -823,24 +857,32 @@
           <t>2024-08-06</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>334</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-09-05 13:36:45</t>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:51:06</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-06 13:51:06</t>
+          <t>2026-09-07 16:12:10</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-07 16:12:10</t>
+          <t>2026-09-08 14:49:53</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:49:53</t>
+          <t>2026-09-09 14:54:54</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-09 14:54:54</t>
+          <t>2026-09-10 14:42:09</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:42:09</t>
+          <t>2026-09-11 14:42:36</t>
         </is>
       </c>
     </row>

--- a/exports/California_Surplus_Feed.xlsx
+++ b/exports/California_Surplus_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-11 14:42:36</t>
+          <t>2026-09-12 13:48:40</t>
         </is>
       </c>
     </row>
